--- a/information_request_forms/020_property_innovation_hub_contact_form--information_request_forms.xlsx
+++ b/information_request_forms/020_property_innovation_hub_contact_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Apartment'}</t>
+          <t>Apartment</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'house'}</t>
+          <t>house</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'House'}</t>
+          <t>House</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone Call'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'energy_efficiency'}</t>
+          <t>energy_efficiency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Energy Efficiency'}</t>
+          <t>Energy Efficiency</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'water_conservation'}</t>
+          <t>water_conservation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Water Conservation'}</t>
+          <t>Water Conservation</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sustainability'}</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sustainability'}</t>
+          <t>Sustainability</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
